--- a/data/Base_Mensal.xlsx
+++ b/data/Base_Mensal.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,13 +504,13 @@
         <v>37825043.31</v>
       </c>
       <c r="C4" t="n">
-        <v>2066062.45</v>
+        <v>2117164.41</v>
       </c>
       <c r="D4" t="n">
-        <v>980763.12</v>
+        <v>676771.64</v>
       </c>
       <c r="E4" t="n">
-        <v>2.59</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="5">
@@ -523,13 +523,13 @@
         <v>31158805.85</v>
       </c>
       <c r="C5" t="n">
-        <v>2377184.6</v>
+        <v>2493993.48</v>
       </c>
       <c r="D5" t="n">
-        <v>683728.86</v>
+        <v>342778.37</v>
       </c>
       <c r="E5" t="n">
-        <v>2.19</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="6">
@@ -542,13 +542,13 @@
         <v>33077113.66</v>
       </c>
       <c r="C6" t="n">
-        <v>2452772.97</v>
+        <v>2498902.67</v>
       </c>
       <c r="D6" t="n">
-        <v>640719.0600000001</v>
+        <v>528824.0600000001</v>
       </c>
       <c r="E6" t="n">
-        <v>1.94</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="7">
@@ -561,13 +561,13 @@
         <v>27272055.46</v>
       </c>
       <c r="C7" t="n">
-        <v>2210153.48</v>
+        <v>2292641.7</v>
       </c>
       <c r="D7" t="n">
-        <v>633312.34</v>
+        <v>516773.74</v>
       </c>
       <c r="E7" t="n">
-        <v>2.32</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="8">
@@ -580,13 +580,13 @@
         <v>33290828.25</v>
       </c>
       <c r="C8" t="n">
-        <v>2006402.99</v>
+        <v>2006514.79</v>
       </c>
       <c r="D8" t="n">
-        <v>566406.1800000001</v>
+        <v>538696.92</v>
       </c>
       <c r="E8" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="9">
@@ -602,10 +602,10 @@
         <v>2052781.36</v>
       </c>
       <c r="D9" t="n">
-        <v>440203.17</v>
+        <v>407551.87</v>
       </c>
       <c r="E9" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="10">
@@ -618,13 +618,13 @@
         <v>33033084.91</v>
       </c>
       <c r="C10" t="n">
-        <v>2090733.29</v>
+        <v>2090929.09</v>
       </c>
       <c r="D10" t="n">
-        <v>489789.54</v>
+        <v>470142.69</v>
       </c>
       <c r="E10" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="11">
@@ -634,17 +634,87 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>35068190.93</v>
+        <v>38066994.29</v>
       </c>
       <c r="C11" t="n">
-        <v>1938466.39</v>
+        <v>2082398.13</v>
       </c>
       <c r="D11" t="n">
-        <v>208259.26</v>
+        <v>241440.72</v>
       </c>
       <c r="E11" t="n">
-        <v>0.59</v>
-      </c>
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>22419244.32</v>
+      </c>
+      <c r="C12" t="n">
+        <v>492533.62</v>
+      </c>
+      <c r="D12" t="n">
+        <v>13226.08</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" t="n">
+        <v>86319.32000000001</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" t="n">
+        <v>51883.25</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" t="n">
+        <v>539</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -657,7 +727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C149"/>
+  <dimension ref="A1:C111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -835,11 +905,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AMAZON.COM.BR</t>
+          <t>CARVALIMA</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2084.5</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13">
@@ -850,11 +920,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AZUL CARGO</t>
+          <t>ENVIABYBUS</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2088.17</v>
+        <v>400.52</v>
       </c>
     </row>
     <row r="14">
@@ -865,11 +935,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AZUL LINHAS AEREAS</t>
+          <t>FAVORITA</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22419.47</v>
+        <v>633.42</v>
       </c>
     </row>
     <row r="15">
@@ -880,11 +950,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CARRIERS</t>
+          <t>IMILE</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>292.8</v>
+        <v>239522.81</v>
       </c>
     </row>
     <row r="16">
@@ -895,11 +965,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CARVALIMA</t>
+          <t>JADLOG</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>199</v>
+        <v>223997.96</v>
       </c>
     </row>
     <row r="17">
@@ -910,11 +980,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CORREIOS</t>
+          <t>JAMEF</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>297.1</v>
+        <v>48716.99</v>
       </c>
     </row>
     <row r="18">
@@ -925,11 +995,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CORREIOS SEDEX - 34028316000103</t>
+          <t>JET</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2089.69</v>
+        <v>93903.98</v>
       </c>
     </row>
     <row r="19">
@@ -940,11 +1010,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>MAGALU</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1262.86</v>
+        <v>66409.63</v>
       </c>
     </row>
     <row r="20">
@@ -955,677 +1025,677 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ENVIABYBUS</t>
+          <t>TODO BRASIL</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>400.52</v>
+        <v>2987.33</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FAVORITA</t>
+          <t>CARVALIMA</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>633.42</v>
+        <v>4213.25</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>IMILE</t>
+          <t>ENVIABYBUS</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>318660.07</v>
+        <v>15282.46</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>JADLOG</t>
+          <t>FAVORITA</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>270839.6</v>
+        <v>1570.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>JAMEF</t>
+          <t>IMILE</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>50405.57</v>
+        <v>159369.52</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>JET</t>
+          <t>JADLOG</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>168176.96</v>
+        <v>33484.54</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MAGALU</t>
+          <t>JAMEF</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>83368.53999999999</v>
+        <v>32391.74</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>R3 EXPRESS</t>
+          <t>JET</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1656.04</v>
+        <v>51090.22</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>R3 TRANSPORTES</t>
+          <t>MAGALU</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1653.13</v>
+        <v>35914.24</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SHOPEE EXPRESS</t>
+          <t>TODO BRASIL</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>39.9</v>
+        <v>5241.9</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>TODO BRASIL</t>
+          <t>VIA PAJUCARA</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2987.33</v>
+        <v>4220</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>AGILE</t>
+          <t>CARVALIMA</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>34.9</v>
+        <v>281.8</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>AZUL CARGO</t>
+          <t>CORREIOS</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>31.9</v>
+        <v>6411.5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>AZUL LINHAS AEREAS</t>
+          <t>ENVIABYBUS</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>90</v>
+        <v>1336.8</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CARVALIMA</t>
+          <t>FAVORITA</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4213.25</v>
+        <v>18497.71</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CORREIOS</t>
+          <t>GOLLOG</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2159.8</v>
+        <v>23867.46</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CORREIOS SEDEX - 34028316000103</t>
+          <t>IMILE</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>542.4</v>
+        <v>154786.24</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ENVIABYBUS</t>
+          <t>JADLOG</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>15282.46</v>
+        <v>1256.9</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FAVORITA</t>
+          <t>JAMEF</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1570.5</v>
+        <v>120780.84</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>IMILE</t>
+          <t>JET</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>209880.76</v>
+        <v>88884.27</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>JADLOG</t>
+          <t>MAGALU</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>81376.77</v>
+        <v>90593.25999999999</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>JAMEF</t>
+          <t>PACÍFICO</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>42578.01</v>
+        <v>1330.46</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>JET</t>
+          <t>R3 TRANSPORTES</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>83954.46000000001</v>
+        <v>11346.63</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>MAGALU</t>
+          <t>TODO BRASIL</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>80742.57000000001</v>
+        <v>6009.39</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>R3 EXPRESS</t>
+          <t>VIA PAJUCARA</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>399.99</v>
+        <v>3440.8</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>R3 TRANSPORTES</t>
+          <t>CARVALIMA</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>9758.43</v>
+        <v>558.48</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>TODO BRASIL</t>
+          <t>ENVIABYBUS</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>5241.9</v>
+        <v>3205.82</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>TODOBRASIL</t>
+          <t>FAVORITA</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>654.1</v>
+        <v>23190.51</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>VIA PAJUCARA</t>
+          <t>GOLLOG</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>4220</v>
+        <v>38569.31</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>AGILE</t>
+          <t>IMILE</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>152.8</v>
+        <v>231314.33</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>AZUL LINHAS AEREAS</t>
+          <t>JADLOG</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>250.25</v>
+        <v>25662.51</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CARVALIMA</t>
+          <t>JAMEF</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>281.8</v>
+        <v>64840.81</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CORREIOS</t>
+          <t>JET</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>19005.18</v>
+        <v>59715.27</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CORREIOS SEDEX - 34028316000103</t>
+          <t>MAGALU</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>904.75</v>
+        <v>52391.37</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ENVIABYBUS</t>
+          <t>PACÍFICO</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1336.8</v>
+        <v>767</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>FAVORITA</t>
+          <t>R3 TRANSPORTES</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>18497.71</v>
+        <v>15210.43</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>GOLLOG</t>
+          <t>VIA PAJUCARA</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>23867.46</v>
+        <v>1347.9</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>IMILE</t>
+          <t>CARVALIMA</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>163082.24</v>
+        <v>7161.53</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JADLOG</t>
+          <t>ENVIABYBUS</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>39958.8</v>
+        <v>7009</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>JAMEF</t>
+          <t>FAVORITA</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>123678.84</v>
+        <v>6757.07</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>JET</t>
+          <t>GOLLOG</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>103654.04</v>
+        <v>27222.1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>MAGALU</t>
+          <t>IMILE</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>91164.74000000001</v>
+        <v>238910.16</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MERCADO LIVRE</t>
+          <t>JAMEF</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1450.86</v>
+        <v>71895.68000000001</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PACÍFICO</t>
+          <t>JET</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1330.46</v>
+        <v>121234.73</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PAJUCARA</t>
+          <t>MAGALU</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1139.1</v>
+        <v>44816.63</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1634,613 +1704,613 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>21326.11</v>
+        <v>11880.01</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SHOPEE EXPRESS</t>
+          <t>VIA PAJUCARA</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>2628.95</v>
+        <v>1810.01</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>TODO BRASIL</t>
+          <t>ASAPLOG</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>6009.39</v>
+        <v>96.63</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>TODOBRASIL</t>
+          <t>CARVALIMA</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>8250</v>
+        <v>906.5</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>VIA PAJUCARA</t>
+          <t>CORREIOS</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>3440.8</v>
+        <v>171.82</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>AGILE</t>
+          <t>ENVIABYBUS</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>851</v>
+        <v>639.36</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>AZUL LINHAS AEREAS</t>
+          <t>FAVORITA</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>82.90000000000001</v>
+        <v>1260.88</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>CARVALIMA</t>
+          <t>GOLLOG</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>558.48</v>
+        <v>35469.43</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CORREIOS</t>
+          <t>IMILE</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>62318.97</v>
+        <v>207899.39</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CORREIOS SEDEX - 34028316000103</t>
+          <t>JADLOG</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1927.5</v>
+        <v>52582.22</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ENVIABYBUS</t>
+          <t>JAMEF</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>3205.82</v>
+        <v>68438.01000000001</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>FAVORITA</t>
+          <t>JET</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>23190.51</v>
+        <v>25288.99</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>GOLLOG</t>
+          <t>MAGALU</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>38569.31</v>
+        <v>9748.049999999999</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>IMILE</t>
+          <t>PACÍFICO</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>235243.66</v>
+        <v>1906.81</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>JADLOG</t>
+          <t>R3 TRANSPORTES</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>29887.01</v>
+        <v>3143.76</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>JAMEF</t>
+          <t>VIA PAJUCARA</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>64840.81</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>JET</t>
+          <t>ASAPLOG</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>66530.63</v>
+        <v>36747.08</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>MAGALU</t>
+          <t>CARVALIMA</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>52391.37</v>
+        <v>8774.25</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>MELIATRUS</t>
+          <t>CORREIOS</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>169</v>
+        <v>182.58</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>PACÍFICO</t>
+          <t>FAVORITA</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>767</v>
+        <v>11296.13</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>R3 TRANSPORTES</t>
+          <t>GOLLOG</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>16060.28</v>
+        <v>44112.42</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>STONE</t>
+          <t>IMILE</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>0.01</v>
+        <v>171845.39</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>VIA PAJUCARA</t>
+          <t>JADLOG</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1347.9</v>
+        <v>65855.25999999999</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>AGILE</t>
+          <t>JAMEF</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1222.6</v>
+        <v>70025.8</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>CARVALIMA</t>
+          <t>JET</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>7161.53</v>
+        <v>1849.71</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>CORREIOS</t>
+          <t>LSP</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>16177.13</v>
+        <v>1217.6</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>CORREIOS SEDEX - 34028316000103</t>
+          <t>MAGALU</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>791</v>
+        <v>51656.82</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ENVIABYBUS</t>
+          <t>PACÍFICO</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>7009</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>FAVORITA</t>
+          <t>R3 TRANSPORTES</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>6757.07</v>
+        <v>5780.64</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>GOLLOG</t>
+          <t>STONE ENTREGA</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>27222.1</v>
+        <v>799</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>IMILE</t>
+          <t>ANJUN EXPRESS</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>239932.06</v>
+        <v>203.7</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>JADLOG</t>
+          <t>ASAPLOG</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>6459.9</v>
+        <v>8749.07</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>JAMEF</t>
+          <t>CARVALIMA</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>73009.78</v>
+        <v>581.89</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>JET</t>
+          <t>CORREIOS</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>121583.38</v>
+        <v>110.3</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>MAGALU</t>
+          <t>FAVORITA</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>44816.63</v>
+        <v>4916.48</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>R3 TRANSPORTES</t>
+          <t>GOLLOG</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>11880.01</v>
+        <v>40183.36</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>VIA PAJUCARA</t>
+          <t>IMILE</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1810.01</v>
+        <v>93213.77</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>AGILE</t>
+          <t>JADLOG</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>2941.14</v>
+        <v>9318.190000000001</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>ASAPLOG</t>
+          <t>JAMEF</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>96.63</v>
+        <v>58562.87</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>AZUL CARGO</t>
+          <t>MAGALU</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>55.95</v>
+        <v>17019.26</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>CARVALIMA</t>
+          <t>R3 TRANSPORTES</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>906.5</v>
+        <v>8581.83</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2249,652 +2319,82 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>13917.5</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>ENVIABYBUS</t>
+          <t>GOLLOG</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>639.36</v>
+        <v>5745.58</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>FAVORITA</t>
+          <t>IMILE</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1260.88</v>
+        <v>1864.2</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>GOLLOG</t>
+          <t>JAMEF</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>35469.43</v>
+        <v>4619.91</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>IMILE</t>
+          <t>MAGALU</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>207716.42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>JADLOG</t>
+          <t>R3 TRANSPORTES</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>52121.95</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>JAMEF</t>
-        </is>
-      </c>
-      <c r="C112" t="n">
-        <v>68438.01000000001</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>JET</t>
-        </is>
-      </c>
-      <c r="C113" t="n">
-        <v>32432.82</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>MAGALU</t>
-        </is>
-      </c>
-      <c r="C114" t="n">
-        <v>9883.049999999999</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>PACÍFICO</t>
-        </is>
-      </c>
-      <c r="C115" t="n">
-        <v>1906.81</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>R3 TRANSPORTES</t>
-        </is>
-      </c>
-      <c r="C116" t="n">
-        <v>3143.76</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>VIA PAJUCARA</t>
-        </is>
-      </c>
-      <c r="C117" t="n">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>AGILE</t>
-        </is>
-      </c>
-      <c r="C118" t="n">
-        <v>685.78</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>ASAPLOG</t>
-        </is>
-      </c>
-      <c r="C119" t="n">
-        <v>31639.13</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>ATRUS INTERMEDIACAO</t>
-        </is>
-      </c>
-      <c r="C120" t="n">
-        <v>318.72</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>AZUL CARGO</t>
-        </is>
-      </c>
-      <c r="C121" t="n">
-        <v>6640.28</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>CARVALIMA</t>
-        </is>
-      </c>
-      <c r="C122" t="n">
-        <v>9825.09</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>CORREIOS</t>
-        </is>
-      </c>
-      <c r="C123" t="n">
-        <v>8619.08</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>CORREIOS SEDEX - 34028316000103</t>
-        </is>
-      </c>
-      <c r="C124" t="n">
-        <v>385.5</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>FAVORITA</t>
-        </is>
-      </c>
-      <c r="C125" t="n">
-        <v>11296.13</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>GOLLOG</t>
-        </is>
-      </c>
-      <c r="C126" t="n">
-        <v>43896.72</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>IMILE</t>
-        </is>
-      </c>
-      <c r="C127" t="n">
-        <v>147505.41</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>JADLOG</t>
-        </is>
-      </c>
-      <c r="C128" t="n">
-        <v>55603.78</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>JAMEF</t>
-        </is>
-      </c>
-      <c r="C129" t="n">
-        <v>46297.39</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>JET</t>
-        </is>
-      </c>
-      <c r="C130" t="n">
-        <v>69800.42</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>LSP</t>
-        </is>
-      </c>
-      <c r="C131" t="n">
-        <v>717.61</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>MAGALU</t>
-        </is>
-      </c>
-      <c r="C132" t="n">
-        <v>46669.84</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>PACÍFICO</t>
-        </is>
-      </c>
-      <c r="C133" t="n">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>R3 EXPRESS</t>
-        </is>
-      </c>
-      <c r="C134" t="n">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>R3 TRANSPORTES</t>
-        </is>
-      </c>
-      <c r="C135" t="n">
-        <v>5780.64</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>SHOPEE EXPRESS</t>
-        </is>
-      </c>
-      <c r="C136" t="n">
-        <v>41.8</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>STONE ENTREGA</t>
-        </is>
-      </c>
-      <c r="C137" t="n">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>AGILE</t>
-        </is>
-      </c>
-      <c r="C138" t="n">
-        <v>440.44</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>ANJUN EXPRESS</t>
-        </is>
-      </c>
-      <c r="C139" t="n">
-        <v>203.7</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>ASAPLOG</t>
-        </is>
-      </c>
-      <c r="C140" t="n">
-        <v>2721.38</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>AZUL CARGO</t>
-        </is>
-      </c>
-      <c r="C141" t="n">
-        <v>46647.95</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>CORREIOS</t>
-        </is>
-      </c>
-      <c r="C142" t="n">
-        <v>2236.76</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>GOLLOG</t>
-        </is>
-      </c>
-      <c r="C143" t="n">
-        <v>13101.08</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>IMILE</t>
-        </is>
-      </c>
-      <c r="C144" t="n">
-        <v>28949.21</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>JADLOG</t>
-        </is>
-      </c>
-      <c r="C145" t="n">
-        <v>43286.99</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>JAMEF</t>
-        </is>
-      </c>
-      <c r="C146" t="n">
-        <v>8927.030000000001</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>JET</t>
-        </is>
-      </c>
-      <c r="C147" t="n">
-        <v>46161.5</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>MAGALU</t>
-        </is>
-      </c>
-      <c r="C148" t="n">
-        <v>7322.33</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>R3 TRANSPORTES</t>
-        </is>
-      </c>
-      <c r="C149" t="n">
-        <v>3501.66</v>
+        <v>956.38</v>
       </c>
     </row>
   </sheetData>

--- a/data/Base_Mensal.xlsx
+++ b/data/Base_Mensal.xlsx
@@ -469,7 +469,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>124014.97</v>
+        <v>125455.47</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -507,10 +507,10 @@
         <v>2117164.41</v>
       </c>
       <c r="D4" t="n">
-        <v>676771.64</v>
+        <v>717227.79</v>
       </c>
       <c r="E4" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="5">
@@ -526,10 +526,10 @@
         <v>2493993.48</v>
       </c>
       <c r="D5" t="n">
-        <v>342778.37</v>
+        <v>358279.9</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="6">
@@ -545,10 +545,10 @@
         <v>2498902.67</v>
       </c>
       <c r="D6" t="n">
-        <v>528824.0600000001</v>
+        <v>545511.17</v>
       </c>
       <c r="E6" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="7">
@@ -564,10 +564,10 @@
         <v>2292641.7</v>
       </c>
       <c r="D7" t="n">
-        <v>516773.74</v>
+        <v>569314.37</v>
       </c>
       <c r="E7" t="n">
-        <v>1.89</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="8">
@@ -583,10 +583,10 @@
         <v>2006514.79</v>
       </c>
       <c r="D8" t="n">
-        <v>538696.92</v>
+        <v>559348.4399999999</v>
       </c>
       <c r="E8" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="9">
@@ -602,10 +602,10 @@
         <v>2052781.36</v>
       </c>
       <c r="D9" t="n">
-        <v>407551.87</v>
+        <v>437165.1</v>
       </c>
       <c r="E9" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="10">
@@ -621,10 +621,10 @@
         <v>2090929.09</v>
       </c>
       <c r="D10" t="n">
-        <v>470142.69</v>
+        <v>500332.81</v>
       </c>
       <c r="E10" t="n">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="11">
@@ -640,10 +640,10 @@
         <v>2082398.13</v>
       </c>
       <c r="D11" t="n">
-        <v>241440.72</v>
+        <v>246261.5</v>
       </c>
       <c r="E11" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="12">
@@ -659,10 +659,10 @@
         <v>492533.62</v>
       </c>
       <c r="D12" t="n">
-        <v>13226.08</v>
+        <v>19674.24</v>
       </c>
       <c r="E12" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="13">
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17547.47</v>
+        <v>17903.25</v>
       </c>
     </row>
     <row r="5">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>42402</v>
+        <v>42679.02</v>
       </c>
     </row>
     <row r="6">
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>31697.7</v>
+        <v>31732.6</v>
       </c>
     </row>
     <row r="7">
@@ -834,7 +834,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>26987.67</v>
+        <v>27760.47</v>
       </c>
     </row>
     <row r="8">
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>239522.81</v>
+        <v>245904.16</v>
       </c>
     </row>
     <row r="16">
@@ -969,7 +969,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>223997.96</v>
+        <v>252185.07</v>
       </c>
     </row>
     <row r="17">
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>93903.98</v>
+        <v>97191.64999999999</v>
       </c>
     </row>
     <row r="19">
@@ -1014,7 +1014,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>66409.63</v>
+        <v>69009.64999999999</v>
       </c>
     </row>
     <row r="20">
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>159369.52</v>
+        <v>167884.35</v>
       </c>
     </row>
     <row r="25">
@@ -1104,7 +1104,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>33484.54</v>
+        <v>35719</v>
       </c>
     </row>
     <row r="26">
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>32391.74</v>
+        <v>32391.75</v>
       </c>
     </row>
     <row r="27">
@@ -1134,7 +1134,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>51090.22</v>
+        <v>54003.44</v>
       </c>
     </row>
     <row r="28">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>35914.24</v>
+        <v>37753.25</v>
       </c>
     </row>
     <row r="29">
@@ -1209,7 +1209,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>6411.5</v>
+        <v>6761.5</v>
       </c>
     </row>
     <row r="33">
@@ -1254,7 +1254,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>23867.46</v>
+        <v>25074.46</v>
       </c>
     </row>
     <row r="36">
@@ -1269,7 +1269,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>154786.24</v>
+        <v>163319.48</v>
       </c>
     </row>
     <row r="37">
@@ -1299,7 +1299,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>120780.84</v>
+        <v>120834.9</v>
       </c>
     </row>
     <row r="39">
@@ -1314,7 +1314,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>88884.27</v>
+        <v>92943.61</v>
       </c>
     </row>
     <row r="40">
@@ -1329,7 +1329,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>90593.25999999999</v>
+        <v>93076.73</v>
       </c>
     </row>
     <row r="41">
@@ -1404,7 +1404,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>558.48</v>
+        <v>881.24</v>
       </c>
     </row>
     <row r="46">
@@ -1434,7 +1434,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>23190.51</v>
+        <v>31643.06</v>
       </c>
     </row>
     <row r="48">
@@ -1449,7 +1449,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>38569.31</v>
+        <v>50068.36</v>
       </c>
     </row>
     <row r="49">
@@ -1464,7 +1464,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>231314.33</v>
+        <v>240309.42</v>
       </c>
     </row>
     <row r="50">
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>25662.51</v>
+        <v>26048.01</v>
       </c>
     </row>
     <row r="51">
@@ -1494,7 +1494,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>64840.81</v>
+        <v>70477.74000000001</v>
       </c>
     </row>
     <row r="52">
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>59715.27</v>
+        <v>69158.66</v>
       </c>
     </row>
     <row r="53">
@@ -1524,7 +1524,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>52391.37</v>
+        <v>56905.32</v>
       </c>
     </row>
     <row r="54">
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>767</v>
+        <v>3928.51</v>
       </c>
     </row>
     <row r="55">
@@ -1554,7 +1554,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>15210.43</v>
+        <v>15340.33</v>
       </c>
     </row>
     <row r="56">
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>6757.07</v>
+        <v>8056.97</v>
       </c>
     </row>
     <row r="60">
@@ -1629,7 +1629,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>27222.1</v>
+        <v>27716.49</v>
       </c>
     </row>
     <row r="61">
@@ -1644,7 +1644,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>238910.16</v>
+        <v>246071.94</v>
       </c>
     </row>
     <row r="62">
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>71895.68000000001</v>
+        <v>78075.17999999999</v>
       </c>
     </row>
     <row r="63">
@@ -1674,7 +1674,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>121234.73</v>
+        <v>125443.16</v>
       </c>
     </row>
     <row r="64">
@@ -1689,7 +1689,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>44816.63</v>
+        <v>46124.15</v>
       </c>
     </row>
     <row r="65">
@@ -1749,7 +1749,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>906.5</v>
+        <v>9026.459999999999</v>
       </c>
     </row>
     <row r="69">
@@ -1764,7 +1764,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>171.82</v>
+        <v>171.83</v>
       </c>
     </row>
     <row r="70">
@@ -1809,7 +1809,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>35469.43</v>
+        <v>48821.12</v>
       </c>
     </row>
     <row r="73">
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>207899.39</v>
+        <v>212229.38</v>
       </c>
     </row>
     <row r="74">
@@ -1839,7 +1839,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>52582.22</v>
+        <v>55137.07</v>
       </c>
     </row>
     <row r="75">
@@ -1869,7 +1869,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>25288.99</v>
+        <v>26545.68</v>
       </c>
     </row>
     <row r="77">
@@ -1884,7 +1884,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>9748.049999999999</v>
+        <v>9748.09</v>
       </c>
     </row>
     <row r="78">
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>36747.08</v>
+        <v>40088.45</v>
       </c>
     </row>
     <row r="82">
@@ -1959,7 +1959,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>8774.25</v>
+        <v>10124.29</v>
       </c>
     </row>
     <row r="83">
@@ -2004,7 +2004,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>44112.42</v>
+        <v>45205.72</v>
       </c>
     </row>
     <row r="86">
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>171845.39</v>
+        <v>173404.25</v>
       </c>
     </row>
     <row r="87">
@@ -2034,7 +2034,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>65855.25999999999</v>
+        <v>65916.70999999999</v>
       </c>
     </row>
     <row r="88">
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>70025.8</v>
+        <v>91574.8</v>
       </c>
     </row>
     <row r="89">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>51656.82</v>
+        <v>52892.92</v>
       </c>
     </row>
     <row r="92">
@@ -2169,7 +2169,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>8749.07</v>
+        <v>8986.4</v>
       </c>
     </row>
     <row r="97">
@@ -2229,7 +2229,7 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>40183.36</v>
+        <v>40251.81</v>
       </c>
     </row>
     <row r="101">
@@ -2244,7 +2244,7 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>93213.77</v>
+        <v>94528.77</v>
       </c>
     </row>
     <row r="102">
@@ -2274,7 +2274,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>58562.87</v>
+        <v>60562.87</v>
       </c>
     </row>
     <row r="104">
@@ -2289,7 +2289,7 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>17019.26</v>
+        <v>17319.27</v>
       </c>
     </row>
     <row r="105">
@@ -2304,7 +2304,7 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>8581.83</v>
+        <v>9481.82</v>
       </c>
     </row>
     <row r="106">
@@ -2334,7 +2334,7 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>5745.58</v>
+        <v>11167.24</v>
       </c>
     </row>
     <row r="108">
@@ -2349,7 +2349,7 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1864.2</v>
+        <v>1964.2</v>
       </c>
     </row>
     <row r="109">
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>4619.91</v>
+        <v>4619.92</v>
       </c>
     </row>
     <row r="110">
@@ -2394,7 +2394,7 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>956.38</v>
+        <v>1882.87</v>
       </c>
     </row>
   </sheetData>

--- a/data/Base_Mensal.xlsx
+++ b/data/Base_Mensal.xlsx
@@ -504,7 +504,7 @@
         <v>37825043.31</v>
       </c>
       <c r="C4" t="n">
-        <v>2117164.41</v>
+        <v>2164847.78</v>
       </c>
       <c r="D4" t="n">
         <v>717227.79</v>
@@ -523,7 +523,7 @@
         <v>31158805.85</v>
       </c>
       <c r="C5" t="n">
-        <v>2493993.48</v>
+        <v>2520347.06</v>
       </c>
       <c r="D5" t="n">
         <v>358279.9</v>
@@ -564,7 +564,7 @@
         <v>2292641.7</v>
       </c>
       <c r="D7" t="n">
-        <v>569314.37</v>
+        <v>569360.3199999999</v>
       </c>
       <c r="E7" t="n">
         <v>2.09</v>
@@ -580,7 +580,7 @@
         <v>33290828.25</v>
       </c>
       <c r="C8" t="n">
-        <v>2006514.79</v>
+        <v>2107462.07</v>
       </c>
       <c r="D8" t="n">
         <v>559348.4399999999</v>
@@ -602,10 +602,10 @@
         <v>2052781.36</v>
       </c>
       <c r="D9" t="n">
-        <v>437165.1</v>
+        <v>440103.17</v>
       </c>
       <c r="E9" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="10">
@@ -621,10 +621,10 @@
         <v>2090929.09</v>
       </c>
       <c r="D10" t="n">
-        <v>500332.81</v>
+        <v>533560.51</v>
       </c>
       <c r="E10" t="n">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="11">
@@ -640,10 +640,10 @@
         <v>2082398.13</v>
       </c>
       <c r="D11" t="n">
-        <v>246261.5</v>
+        <v>338743.5</v>
       </c>
       <c r="E11" t="n">
-        <v>0.65</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="12">
@@ -656,13 +656,13 @@
         <v>22419244.32</v>
       </c>
       <c r="C12" t="n">
-        <v>492533.62</v>
+        <v>1031701.73</v>
       </c>
       <c r="D12" t="n">
-        <v>19674.24</v>
+        <v>156258.11</v>
       </c>
       <c r="E12" t="n">
-        <v>0.09</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="13">
@@ -727,7 +727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C111"/>
+  <dimension ref="A1:C115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1464,7 +1464,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>240309.42</v>
+        <v>240355.37</v>
       </c>
     </row>
     <row r="50">
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>212229.38</v>
+        <v>213450.67</v>
       </c>
     </row>
     <row r="74">
@@ -1839,7 +1839,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>55137.07</v>
+        <v>56853.85</v>
       </c>
     </row>
     <row r="75">
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>40088.45</v>
+        <v>41685.99</v>
       </c>
     </row>
     <row r="82">
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>173404.25</v>
+        <v>189720.42</v>
       </c>
     </row>
     <row r="87">
@@ -2034,7 +2034,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>65916.70999999999</v>
+        <v>72459.61</v>
       </c>
     </row>
     <row r="88">
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>91574.8</v>
+        <v>100156.7</v>
       </c>
     </row>
     <row r="89">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>52892.92</v>
+        <v>53082.11</v>
       </c>
     </row>
     <row r="92">
@@ -2154,7 +2154,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>203.7</v>
+        <v>293.5</v>
       </c>
     </row>
     <row r="96">
@@ -2169,7 +2169,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>8986.4</v>
+        <v>19248.06</v>
       </c>
     </row>
     <row r="97">
@@ -2199,7 +2199,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>110.3</v>
+        <v>200.25</v>
       </c>
     </row>
     <row r="99">
@@ -2229,7 +2229,7 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>40251.81</v>
+        <v>40514.61</v>
       </c>
     </row>
     <row r="101">
@@ -2244,7 +2244,7 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>94528.77</v>
+        <v>161208.25</v>
       </c>
     </row>
     <row r="102">
@@ -2259,7 +2259,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>9318.190000000001</v>
+        <v>17530.24</v>
       </c>
     </row>
     <row r="103">
@@ -2274,7 +2274,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>60562.87</v>
+        <v>62712.87</v>
       </c>
     </row>
     <row r="104">
@@ -2289,7 +2289,7 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>17319.27</v>
+        <v>18915.49</v>
       </c>
     </row>
     <row r="105">
@@ -2304,22 +2304,22 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>9481.82</v>
+        <v>12551.86</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>CORREIOS</t>
+          <t>VIA PAJUCARA</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>0.01</v>
+        <v>70</v>
       </c>
     </row>
     <row r="107">
@@ -2330,11 +2330,11 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>GOLLOG</t>
+          <t>CORREIOS</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>11167.24</v>
+        <v>124.71</v>
       </c>
     </row>
     <row r="108">
@@ -2345,11 +2345,11 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>IMILE</t>
+          <t>GOLLOG</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>1964.2</v>
+        <v>16856.5</v>
       </c>
     </row>
     <row r="109">
@@ -2360,11 +2360,11 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>JAMEF</t>
+          <t>IMILE</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>4619.92</v>
+        <v>54370.2</v>
       </c>
     </row>
     <row r="110">
@@ -2375,11 +2375,11 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>MAGALU</t>
+          <t>JADLOG</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>40</v>
+        <v>3700.7</v>
       </c>
     </row>
     <row r="111">
@@ -2390,11 +2390,71 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
+          <t>JAMEF</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>59477.06</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>LSP</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>MAGALU</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>3511.03</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
           <t>R3 TRANSPORTES</t>
         </is>
       </c>
-      <c r="C111" t="n">
-        <v>1882.87</v>
+      <c r="C114" t="n">
+        <v>16538.11</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>VIA PAJUCARA</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>649.8</v>
       </c>
     </row>
   </sheetData>

--- a/data/Base_Mensal.xlsx
+++ b/data/Base_Mensal.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,9 +471,7 @@
       <c r="D2" t="n">
         <v>125455.47</v>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -490,9 +488,7 @@
       <c r="D3" t="n">
         <v>187.8</v>
       </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
+      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -681,40 +677,6 @@
         <v>0</v>
       </c>
       <c r="E13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-11</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>51883.25</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-12</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>539</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
